--- a/полезно.xlsx
+++ b/полезно.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\irina.mashkova\Documents\GitHub\College\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01553B3-6572-4B78-BCC9-A544887CEEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEF6438-4AF6-458A-BA02-24B63D8DA362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="332" firstSheet="1" activeTab="3" xr2:uid="{626BA957-AA12-44BE-A960-46A94CAF7B15}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="604" firstSheet="1" activeTab="4" xr2:uid="{626BA957-AA12-44BE-A960-46A94CAF7B15}"/>
   </bookViews>
   <sheets>
     <sheet name="пользователи" sheetId="1" r:id="rId1"/>
     <sheet name="техническая" sheetId="2" r:id="rId2"/>
     <sheet name="учебный план" sheetId="3" r:id="rId3"/>
     <sheet name="расписание" sheetId="4" r:id="rId4"/>
+    <sheet name="экзамены" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="261">
   <si>
     <t>Ахремова</t>
   </si>
@@ -816,6 +817,75 @@
   <si>
     <t>экз</t>
   </si>
+  <si>
+    <t>по 13.12 учёба</t>
+  </si>
+  <si>
+    <t>CRD</t>
+  </si>
+  <si>
+    <t>EXM</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>SAT</t>
+  </si>
+  <si>
+    <t>А-100</t>
+  </si>
+  <si>
+    <t>Лекционная аудитория</t>
+  </si>
+  <si>
+    <t>А-305</t>
+  </si>
+  <si>
+    <t>Аудитория для лабораторных работ по физике</t>
+  </si>
+  <si>
+    <t>А-306</t>
+  </si>
+  <si>
+    <t>К-207</t>
+  </si>
+  <si>
+    <t>Аудитория</t>
+  </si>
+  <si>
+    <t>К-208</t>
+  </si>
+  <si>
+    <t>В-209</t>
+  </si>
+  <si>
+    <t>Компьютерная аудитория</t>
+  </si>
+  <si>
+    <t>К-710</t>
+  </si>
+  <si>
+    <t>Г-410</t>
+  </si>
+  <si>
+    <t>Г-411</t>
+  </si>
+  <si>
+    <t>А-303</t>
+  </si>
+  <si>
+    <t>СК</t>
+  </si>
+  <si>
+    <t>Спортивный комплекс</t>
+  </si>
+  <si>
+    <t>nextval('curriculum_lessons_curriculum_lesson_id_seq')</t>
+  </si>
 </sst>
 </file>
 
@@ -1047,6 +1117,121 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>615897</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F319D95-C1D6-46B3-90E0-D0DFE1ADAAB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9441180" y="121920"/>
+          <a:ext cx="3906044" cy="3985260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>531495</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>554355</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>158115</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Прямоугольник 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A15D5143-B8F4-F586-FF6D-9E9B158923C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9389745" y="1733550"/>
+          <a:ext cx="3213735" cy="1139190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34803,4 +34988,1567 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9124A-28A5-44BD-AC91-7F87CF92298E}">
+  <dimension ref="B2:AB55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="H2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>203</v>
+      </c>
+      <c r="K5" t="s">
+        <v>237</v>
+      </c>
+      <c r="L5" s="23">
+        <v>45651</v>
+      </c>
+      <c r="M5" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>198</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K6" t="s">
+        <v>237</v>
+      </c>
+      <c r="L6" s="23">
+        <v>45649</v>
+      </c>
+      <c r="M6" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>205</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
+        <v>197</v>
+      </c>
+      <c r="L7" s="23">
+        <v>45643</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>199</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L8" s="23">
+        <v>45653</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>196</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>205</v>
+      </c>
+      <c r="L9" s="23">
+        <v>45643</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>199</v>
+      </c>
+      <c r="L10" s="23">
+        <v>45645</v>
+      </c>
+      <c r="M10" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>200</v>
+      </c>
+      <c r="L11" s="23"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12" t="s">
+        <v>196</v>
+      </c>
+      <c r="K12" t="s">
+        <v>237</v>
+      </c>
+      <c r="L12" s="23">
+        <v>45654</v>
+      </c>
+      <c r="M12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>198</v>
+      </c>
+      <c r="K13" t="s">
+        <v>237</v>
+      </c>
+      <c r="L13" s="23">
+        <v>45652</v>
+      </c>
+      <c r="M13" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>197</v>
+      </c>
+      <c r="I14">
+        <v>9</v>
+      </c>
+      <c r="J14" t="s">
+        <v>200</v>
+      </c>
+      <c r="L14" s="23">
+        <v>45646</v>
+      </c>
+      <c r="M14" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15" t="s">
+        <v>204</v>
+      </c>
+      <c r="K15" t="s">
+        <v>237</v>
+      </c>
+      <c r="L15" s="23">
+        <v>45649</v>
+      </c>
+      <c r="M15" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="I16">
+        <v>11</v>
+      </c>
+      <c r="J16" t="s">
+        <v>205</v>
+      </c>
+      <c r="L16" s="23">
+        <v>45643</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I17">
+        <v>12</v>
+      </c>
+      <c r="J17" t="s">
+        <v>197</v>
+      </c>
+      <c r="L17" s="23">
+        <v>45643</v>
+      </c>
+      <c r="M17">
+        <v>9</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="3">
+        <v>9.1</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="3">
+        <v>6</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D21" s="3">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>201</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>202</v>
+      </c>
+      <c r="D23" s="3">
+        <v>7</v>
+      </c>
+      <c r="X23" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>203</v>
+      </c>
+      <c r="D24" s="3">
+        <v>8</v>
+      </c>
+      <c r="X24" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3">
+        <v>8</v>
+      </c>
+      <c r="O28" t="s">
+        <v>240</v>
+      </c>
+      <c r="P28">
+        <v>2</v>
+      </c>
+      <c r="T28" s="23">
+        <v>45651</v>
+      </c>
+      <c r="U28" t="s">
+        <v>230</v>
+      </c>
+      <c r="V28" t="s">
+        <v>242</v>
+      </c>
+      <c r="W28">
+        <v>7</v>
+      </c>
+      <c r="X28">
+        <v>29</v>
+      </c>
+      <c r="Y28">
+        <v>2</v>
+      </c>
+      <c r="Z28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29" s="3">
+        <v>12</v>
+      </c>
+      <c r="O29" t="s">
+        <v>240</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="T29" s="23">
+        <v>45649</v>
+      </c>
+      <c r="U29" t="s">
+        <v>228</v>
+      </c>
+      <c r="V29" t="s">
+        <v>242</v>
+      </c>
+      <c r="W29">
+        <v>7</v>
+      </c>
+      <c r="X29">
+        <v>30</v>
+      </c>
+      <c r="Y29">
+        <v>2</v>
+      </c>
+      <c r="Z29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" t="s">
+        <v>245</v>
+      </c>
+      <c r="M30">
+        <v>3</v>
+      </c>
+      <c r="N30">
+        <v>10</v>
+      </c>
+      <c r="O30" t="s">
+        <v>239</v>
+      </c>
+      <c r="P30">
+        <v>2</v>
+      </c>
+      <c r="T30" s="23">
+        <v>45643</v>
+      </c>
+      <c r="U30" t="s">
+        <v>229</v>
+      </c>
+      <c r="V30" t="s">
+        <v>241</v>
+      </c>
+      <c r="W30">
+        <v>4</v>
+      </c>
+      <c r="X30">
+        <v>31</v>
+      </c>
+      <c r="Y30">
+        <v>2</v>
+      </c>
+      <c r="Z30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>246</v>
+      </c>
+      <c r="D31" t="s">
+        <v>247</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31" s="3">
+        <v>3</v>
+      </c>
+      <c r="O31" t="s">
+        <v>240</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="T31" s="23">
+        <v>45653</v>
+      </c>
+      <c r="U31" t="s">
+        <v>232</v>
+      </c>
+      <c r="V31" t="s">
+        <v>242</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>32</v>
+      </c>
+      <c r="Y31">
+        <v>2</v>
+      </c>
+      <c r="Z31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" t="s">
+        <v>247</v>
+      </c>
+      <c r="M32">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
+        <v>11</v>
+      </c>
+      <c r="O32" t="s">
+        <v>239</v>
+      </c>
+      <c r="P32">
+        <v>2</v>
+      </c>
+      <c r="T32" s="23">
+        <v>45643</v>
+      </c>
+      <c r="U32" t="s">
+        <v>229</v>
+      </c>
+      <c r="V32" t="s">
+        <v>241</v>
+      </c>
+      <c r="W32">
+        <v>11</v>
+      </c>
+      <c r="X32">
+        <v>33</v>
+      </c>
+      <c r="Y32">
+        <v>4</v>
+      </c>
+      <c r="Z32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>249</v>
+      </c>
+      <c r="D33" t="s">
+        <v>250</v>
+      </c>
+      <c r="M33">
+        <v>6</v>
+      </c>
+      <c r="N33" s="3">
+        <v>6</v>
+      </c>
+      <c r="O33" t="s">
+        <v>239</v>
+      </c>
+      <c r="P33">
+        <v>2</v>
+      </c>
+      <c r="T33" s="23">
+        <v>45645</v>
+      </c>
+      <c r="U33" t="s">
+        <v>231</v>
+      </c>
+      <c r="V33" t="s">
+        <v>241</v>
+      </c>
+      <c r="W33">
+        <v>5</v>
+      </c>
+      <c r="X33">
+        <v>34</v>
+      </c>
+      <c r="Y33">
+        <v>2</v>
+      </c>
+      <c r="Z33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>251</v>
+      </c>
+      <c r="D34" t="s">
+        <v>250</v>
+      </c>
+      <c r="T34" s="23"/>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>252</v>
+      </c>
+      <c r="D35" t="s">
+        <v>253</v>
+      </c>
+      <c r="M35">
+        <v>7</v>
+      </c>
+      <c r="N35">
+        <v>5</v>
+      </c>
+      <c r="O35" t="s">
+        <v>240</v>
+      </c>
+      <c r="P35">
+        <v>2</v>
+      </c>
+      <c r="T35" s="23">
+        <v>45654</v>
+      </c>
+      <c r="U35" t="s">
+        <v>243</v>
+      </c>
+      <c r="V35" t="s">
+        <v>242</v>
+      </c>
+      <c r="W35">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>35</v>
+      </c>
+      <c r="Y35">
+        <v>2</v>
+      </c>
+      <c r="Z35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>254</v>
+      </c>
+      <c r="D36" t="s">
+        <v>253</v>
+      </c>
+      <c r="M36">
+        <v>8</v>
+      </c>
+      <c r="N36" s="3">
+        <v>3</v>
+      </c>
+      <c r="O36" t="s">
+        <v>240</v>
+      </c>
+      <c r="P36">
+        <v>2</v>
+      </c>
+      <c r="T36" s="23">
+        <v>45652</v>
+      </c>
+      <c r="U36" t="s">
+        <v>231</v>
+      </c>
+      <c r="V36" t="s">
+        <v>242</v>
+      </c>
+      <c r="W36">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>36</v>
+      </c>
+      <c r="Y36">
+        <v>2</v>
+      </c>
+      <c r="Z36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>255</v>
+      </c>
+      <c r="D37" t="s">
+        <v>245</v>
+      </c>
+      <c r="M37">
+        <v>9</v>
+      </c>
+      <c r="N37" s="3">
+        <v>6</v>
+      </c>
+      <c r="O37" t="s">
+        <v>239</v>
+      </c>
+      <c r="P37">
+        <v>2</v>
+      </c>
+      <c r="T37" s="23">
+        <v>45646</v>
+      </c>
+      <c r="U37" t="s">
+        <v>232</v>
+      </c>
+      <c r="V37" t="s">
+        <v>241</v>
+      </c>
+      <c r="W37">
+        <v>5</v>
+      </c>
+      <c r="X37">
+        <v>37</v>
+      </c>
+      <c r="Y37">
+        <v>2</v>
+      </c>
+      <c r="Z37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
+        <v>256</v>
+      </c>
+      <c r="D38" t="s">
+        <v>245</v>
+      </c>
+      <c r="M38">
+        <v>10</v>
+      </c>
+      <c r="N38" s="3">
+        <v>8</v>
+      </c>
+      <c r="O38" t="s">
+        <v>240</v>
+      </c>
+      <c r="P38">
+        <v>2</v>
+      </c>
+      <c r="T38" s="23">
+        <v>45649</v>
+      </c>
+      <c r="U38" t="s">
+        <v>228</v>
+      </c>
+      <c r="V38" t="s">
+        <v>242</v>
+      </c>
+      <c r="W38">
+        <v>6</v>
+      </c>
+      <c r="X38">
+        <v>38</v>
+      </c>
+      <c r="Y38">
+        <v>2</v>
+      </c>
+      <c r="Z38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>257</v>
+      </c>
+      <c r="D39" t="s">
+        <v>245</v>
+      </c>
+      <c r="M39">
+        <v>11</v>
+      </c>
+      <c r="N39" s="3">
+        <v>4</v>
+      </c>
+      <c r="O39" t="s">
+        <v>239</v>
+      </c>
+      <c r="P39">
+        <v>2</v>
+      </c>
+      <c r="T39" s="23">
+        <v>45643</v>
+      </c>
+      <c r="U39" t="s">
+        <v>229</v>
+      </c>
+      <c r="V39" t="s">
+        <v>241</v>
+      </c>
+      <c r="W39">
+        <v>11</v>
+      </c>
+      <c r="X39">
+        <v>39</v>
+      </c>
+      <c r="Y39">
+        <v>4</v>
+      </c>
+      <c r="Z39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>258</v>
+      </c>
+      <c r="D40" t="s">
+        <v>259</v>
+      </c>
+      <c r="M40">
+        <v>12</v>
+      </c>
+      <c r="N40">
+        <v>9</v>
+      </c>
+      <c r="O40" t="s">
+        <v>239</v>
+      </c>
+      <c r="P40">
+        <v>2</v>
+      </c>
+      <c r="T40" s="23">
+        <v>45643</v>
+      </c>
+      <c r="U40" t="s">
+        <v>229</v>
+      </c>
+      <c r="V40" t="s">
+        <v>241</v>
+      </c>
+      <c r="W40">
+        <v>5</v>
+      </c>
+      <c r="X40">
+        <v>40</v>
+      </c>
+      <c r="Y40">
+        <v>2</v>
+      </c>
+      <c r="Z40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="L44" t="s">
+        <v>260</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44" s="3">
+        <v>8</v>
+      </c>
+      <c r="O44" t="s">
+        <v>240</v>
+      </c>
+      <c r="P44">
+        <v>2</v>
+      </c>
+      <c r="R44" t="str">
+        <f>"("&amp;L44&amp;", "&amp;M44&amp;", "&amp;N44&amp;", '"&amp;O44&amp;"', "&amp;P44&amp;")"</f>
+        <v>(nextval('curriculum_lessons_curriculum_lesson_id_seq'), 1, 8, 'EXM', 2)</v>
+      </c>
+      <c r="T44" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U44" s="23">
+        <v>45651</v>
+      </c>
+      <c r="V44" t="s">
+        <v>230</v>
+      </c>
+      <c r="W44" t="s">
+        <v>242</v>
+      </c>
+      <c r="X44">
+        <v>7</v>
+      </c>
+      <c r="Y44">
+        <v>29</v>
+      </c>
+      <c r="Z44">
+        <v>6</v>
+      </c>
+      <c r="AB44" t="str">
+        <f>"("&amp;T44&amp;", '"&amp;TEXT(U44,"ДД.ММ.ГГГГ")&amp;"', '"&amp;V44&amp;"', '"&amp;W44&amp;"', "&amp;X44&amp;", "&amp;Y44&amp;", "&amp;Z44&amp;")"</f>
+        <v>(nextval('tt_lesson_tt_lesson_id_seq'), '25.12.2024', 'WED', 'EX', 7, 29, 6)</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="L45" t="s">
+        <v>260</v>
+      </c>
+      <c r="M45">
+        <v>2</v>
+      </c>
+      <c r="N45" s="3">
+        <v>12</v>
+      </c>
+      <c r="O45" t="s">
+        <v>240</v>
+      </c>
+      <c r="P45">
+        <v>2</v>
+      </c>
+      <c r="R45" t="str">
+        <f>", ("&amp;L45&amp;", "&amp;M45&amp;", "&amp;N45&amp;", '"&amp;O45&amp;"', "&amp;P45&amp;")"</f>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 2, 12, 'EXM', 2)</v>
+      </c>
+      <c r="T45" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U45" s="23">
+        <v>45649</v>
+      </c>
+      <c r="V45" t="s">
+        <v>228</v>
+      </c>
+      <c r="W45" t="s">
+        <v>242</v>
+      </c>
+      <c r="X45">
+        <v>7</v>
+      </c>
+      <c r="Y45">
+        <v>30</v>
+      </c>
+      <c r="Z45">
+        <v>6</v>
+      </c>
+      <c r="AB45" t="str">
+        <f>", ("&amp;T45&amp;", '"&amp;TEXT(U45,"ДД.ММ.ГГГГ")&amp;"', '"&amp;V45&amp;"', '"&amp;W45&amp;"', "&amp;X45&amp;", "&amp;Y45&amp;", "&amp;Z45&amp;")"</f>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '23.12.2024', 'MON', 'EX', 7, 30, 6)</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="L46" t="s">
+        <v>260</v>
+      </c>
+      <c r="M46">
+        <v>3</v>
+      </c>
+      <c r="N46">
+        <v>10</v>
+      </c>
+      <c r="O46" t="s">
+        <v>239</v>
+      </c>
+      <c r="P46">
+        <v>2</v>
+      </c>
+      <c r="R46" t="str">
+        <f t="shared" ref="R46:R55" si="0">", ("&amp;L46&amp;", "&amp;M46&amp;", "&amp;N46&amp;", '"&amp;O46&amp;"', "&amp;P46&amp;")"</f>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 3, 10, 'CRD', 2)</v>
+      </c>
+      <c r="T46" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U46" s="23">
+        <v>45643</v>
+      </c>
+      <c r="V46" t="s">
+        <v>229</v>
+      </c>
+      <c r="W46" t="s">
+        <v>241</v>
+      </c>
+      <c r="X46">
+        <v>4</v>
+      </c>
+      <c r="Y46">
+        <v>31</v>
+      </c>
+      <c r="Z46">
+        <v>6</v>
+      </c>
+      <c r="AB46" t="str">
+        <f t="shared" ref="AB46:AB55" si="1">", ("&amp;T46&amp;", '"&amp;TEXT(U46,"ДД.ММ.ГГГГ")&amp;"', '"&amp;V46&amp;"', '"&amp;W46&amp;"', "&amp;X46&amp;", "&amp;Y46&amp;", "&amp;Z46&amp;")"</f>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '17.12.2024', 'TUE', 'CW', 4, 31, 6)</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="L47" t="s">
+        <v>260</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
+        <v>3</v>
+      </c>
+      <c r="O47" t="s">
+        <v>240</v>
+      </c>
+      <c r="P47">
+        <v>2</v>
+      </c>
+      <c r="R47" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 4, 3, 'EXM', 2)</v>
+      </c>
+      <c r="T47" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U47" s="23">
+        <v>45653</v>
+      </c>
+      <c r="V47" t="s">
+        <v>232</v>
+      </c>
+      <c r="W47" t="s">
+        <v>242</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47">
+        <v>32</v>
+      </c>
+      <c r="Z47">
+        <v>6</v>
+      </c>
+      <c r="AB47" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '27.12.2024', 'FRI', 'EX', 1, 32, 6)</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="L48" t="s">
+        <v>260</v>
+      </c>
+      <c r="M48">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
+        <v>11</v>
+      </c>
+      <c r="O48" t="s">
+        <v>239</v>
+      </c>
+      <c r="P48">
+        <v>2</v>
+      </c>
+      <c r="R48" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 5, 11, 'CRD', 2)</v>
+      </c>
+      <c r="T48" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U48" s="23">
+        <v>45643</v>
+      </c>
+      <c r="V48" t="s">
+        <v>229</v>
+      </c>
+      <c r="W48" t="s">
+        <v>241</v>
+      </c>
+      <c r="X48">
+        <v>11</v>
+      </c>
+      <c r="Y48">
+        <v>33</v>
+      </c>
+      <c r="Z48">
+        <v>5</v>
+      </c>
+      <c r="AB48" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '17.12.2024', 'TUE', 'CW', 11, 33, 5)</v>
+      </c>
+    </row>
+    <row r="49" spans="12:28" x14ac:dyDescent="0.3">
+      <c r="L49" t="s">
+        <v>260</v>
+      </c>
+      <c r="M49">
+        <v>6</v>
+      </c>
+      <c r="N49" s="3">
+        <v>6</v>
+      </c>
+      <c r="O49" t="s">
+        <v>239</v>
+      </c>
+      <c r="P49">
+        <v>2</v>
+      </c>
+      <c r="R49" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 6, 6, 'CRD', 2)</v>
+      </c>
+      <c r="T49" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U49" s="23">
+        <v>45645</v>
+      </c>
+      <c r="V49" t="s">
+        <v>231</v>
+      </c>
+      <c r="W49" t="s">
+        <v>241</v>
+      </c>
+      <c r="X49">
+        <v>5</v>
+      </c>
+      <c r="Y49">
+        <v>34</v>
+      </c>
+      <c r="Z49">
+        <v>6</v>
+      </c>
+      <c r="AB49" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '19.12.2024', 'THU', 'CW', 5, 34, 6)</v>
+      </c>
+    </row>
+    <row r="50" spans="12:28" x14ac:dyDescent="0.3">
+      <c r="L50" t="s">
+        <v>260</v>
+      </c>
+      <c r="M50">
+        <v>7</v>
+      </c>
+      <c r="N50">
+        <v>5</v>
+      </c>
+      <c r="O50" t="s">
+        <v>240</v>
+      </c>
+      <c r="P50">
+        <v>2</v>
+      </c>
+      <c r="R50" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 7, 5, 'EXM', 2)</v>
+      </c>
+      <c r="T50" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U50" s="23">
+        <v>45654</v>
+      </c>
+      <c r="V50" t="s">
+        <v>243</v>
+      </c>
+      <c r="W50" t="s">
+        <v>242</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+      <c r="Y50">
+        <v>35</v>
+      </c>
+      <c r="Z50">
+        <v>6</v>
+      </c>
+      <c r="AB50" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '28.12.2024', 'SAT', 'EX', 1, 35, 6)</v>
+      </c>
+    </row>
+    <row r="51" spans="12:28" x14ac:dyDescent="0.3">
+      <c r="L51" t="s">
+        <v>260</v>
+      </c>
+      <c r="M51">
+        <v>8</v>
+      </c>
+      <c r="N51" s="3">
+        <v>3</v>
+      </c>
+      <c r="O51" t="s">
+        <v>240</v>
+      </c>
+      <c r="P51">
+        <v>2</v>
+      </c>
+      <c r="R51" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 8, 3, 'EXM', 2)</v>
+      </c>
+      <c r="T51" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U51" s="23">
+        <v>45652</v>
+      </c>
+      <c r="V51" t="s">
+        <v>231</v>
+      </c>
+      <c r="W51" t="s">
+        <v>242</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51">
+        <v>36</v>
+      </c>
+      <c r="Z51">
+        <v>6</v>
+      </c>
+      <c r="AB51" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '26.12.2024', 'THU', 'EX', 1, 36, 6)</v>
+      </c>
+    </row>
+    <row r="52" spans="12:28" x14ac:dyDescent="0.3">
+      <c r="L52" t="s">
+        <v>260</v>
+      </c>
+      <c r="M52">
+        <v>9</v>
+      </c>
+      <c r="N52" s="3">
+        <v>6</v>
+      </c>
+      <c r="O52" t="s">
+        <v>239</v>
+      </c>
+      <c r="P52">
+        <v>2</v>
+      </c>
+      <c r="R52" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 9, 6, 'CRD', 2)</v>
+      </c>
+      <c r="T52" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U52" s="23">
+        <v>45646</v>
+      </c>
+      <c r="V52" t="s">
+        <v>232</v>
+      </c>
+      <c r="W52" t="s">
+        <v>241</v>
+      </c>
+      <c r="X52">
+        <v>5</v>
+      </c>
+      <c r="Y52">
+        <v>37</v>
+      </c>
+      <c r="Z52">
+        <v>6</v>
+      </c>
+      <c r="AB52" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '20.12.2024', 'FRI', 'CW', 5, 37, 6)</v>
+      </c>
+    </row>
+    <row r="53" spans="12:28" x14ac:dyDescent="0.3">
+      <c r="L53" t="s">
+        <v>260</v>
+      </c>
+      <c r="M53">
+        <v>10</v>
+      </c>
+      <c r="N53" s="3">
+        <v>8</v>
+      </c>
+      <c r="O53" t="s">
+        <v>240</v>
+      </c>
+      <c r="P53">
+        <v>2</v>
+      </c>
+      <c r="R53" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 10, 8, 'EXM', 2)</v>
+      </c>
+      <c r="T53" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U53" s="23">
+        <v>45649</v>
+      </c>
+      <c r="V53" t="s">
+        <v>228</v>
+      </c>
+      <c r="W53" t="s">
+        <v>242</v>
+      </c>
+      <c r="X53">
+        <v>6</v>
+      </c>
+      <c r="Y53">
+        <v>38</v>
+      </c>
+      <c r="Z53">
+        <v>6</v>
+      </c>
+      <c r="AB53" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '23.12.2024', 'MON', 'EX', 6, 38, 6)</v>
+      </c>
+    </row>
+    <row r="54" spans="12:28" x14ac:dyDescent="0.3">
+      <c r="L54" t="s">
+        <v>260</v>
+      </c>
+      <c r="M54">
+        <v>11</v>
+      </c>
+      <c r="N54" s="3">
+        <v>4</v>
+      </c>
+      <c r="O54" t="s">
+        <v>239</v>
+      </c>
+      <c r="P54">
+        <v>2</v>
+      </c>
+      <c r="R54" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 11, 4, 'CRD', 2)</v>
+      </c>
+      <c r="T54" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U54" s="23">
+        <v>45643</v>
+      </c>
+      <c r="V54" t="s">
+        <v>229</v>
+      </c>
+      <c r="W54" t="s">
+        <v>241</v>
+      </c>
+      <c r="X54">
+        <v>11</v>
+      </c>
+      <c r="Y54">
+        <v>39</v>
+      </c>
+      <c r="Z54">
+        <v>5</v>
+      </c>
+      <c r="AB54" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '17.12.2024', 'TUE', 'CW', 11, 39, 5)</v>
+      </c>
+    </row>
+    <row r="55" spans="12:28" x14ac:dyDescent="0.3">
+      <c r="L55" t="s">
+        <v>260</v>
+      </c>
+      <c r="M55">
+        <v>12</v>
+      </c>
+      <c r="N55">
+        <v>9</v>
+      </c>
+      <c r="O55" t="s">
+        <v>239</v>
+      </c>
+      <c r="P55">
+        <v>2</v>
+      </c>
+      <c r="R55" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('curriculum_lessons_curriculum_lesson_id_seq'), 12, 9, 'CRD', 2)</v>
+      </c>
+      <c r="T55" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="U55" s="23">
+        <v>45643</v>
+      </c>
+      <c r="V55" t="s">
+        <v>229</v>
+      </c>
+      <c r="W55" t="s">
+        <v>241</v>
+      </c>
+      <c r="X55">
+        <v>5</v>
+      </c>
+      <c r="Y55">
+        <v>40</v>
+      </c>
+      <c r="Z55">
+        <v>6</v>
+      </c>
+      <c r="AB55" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('tt_lesson_tt_lesson_id_seq'), '17.12.2024', 'TUE', 'CW', 5, 40, 6)</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B16:D16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>